--- a/resources/quest/quest.xlsx
+++ b/resources/quest/quest.xlsx
@@ -1438,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="15" customWidth="1" style="33" min="1" max="2"/>
@@ -1506,32 +1506,26 @@
     </row>
     <row r="5" ht="16.5" customHeight="1" s="8">
       <c r="A5" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="B5" s="24" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B5" s="24" t="n"/>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>服丹飞升</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>hero_all</t>
-        </is>
-      </c>
+          <t>兽潮来袭·一</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="8">
       <c r="A6" s="23" t="n">
-        <v>251</v>
-      </c>
-      <c r="B6" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="B6" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>以战养战</t>
+          <t>服丹飞升</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -1542,14 +1536,14 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" s="8">
       <c r="A7" s="23" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>炼丹自由</t>
+          <t>以战养战</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -1560,14 +1554,14 @@
     </row>
     <row r="8" ht="16.5" customHeight="1" s="8">
       <c r="A8" s="23" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>道袍加身</t>
+          <t>炼丹自由</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -1578,14 +1572,14 @@
     </row>
     <row r="9" ht="16.5" customHeight="1" s="8">
       <c r="A9" s="23" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>真仙助我</t>
+          <t>道袍加身</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -1596,14 +1590,14 @@
     </row>
     <row r="10" ht="16.5" customHeight="1" s="8">
       <c r="A10" s="23" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>灵气福地</t>
+          <t>真仙助我</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -1614,14 +1608,14 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" s="8">
       <c r="A11" s="23" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>一分为二</t>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>灵气福地</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -1632,17 +1626,17 @@
     </row>
     <row r="12" ht="16.5" customHeight="1" s="8">
       <c r="A12" s="23" t="n">
-        <v>257</v>
-      </c>
-      <c r="B12" s="32" t="n">
+        <v>256</v>
+      </c>
+      <c r="B12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>结束任务测试</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>一分为二</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>hero_all</t>
         </is>
@@ -1650,50 +1644,50 @@
     </row>
     <row r="13" ht="16.5" customHeight="1" s="8">
       <c r="A13" s="23" t="n">
+        <v>257</v>
+      </c>
+      <c r="B13" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>结束任务测试</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>hero_all</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="8">
+      <c r="A14" s="23" t="n">
         <v>258</v>
       </c>
-      <c r="B13" s="33" t="n">
+      <c r="B14" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>打一次灵脉</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>hero_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" s="8">
-      <c r="A14" s="33" t="n">
-        <v>260</v>
-      </c>
-      <c r="B14" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="33" t="inlineStr">
-        <is>
-          <t>增强灵气</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>hero_all</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="8">
       <c r="A15" s="33" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B15" s="33" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>永久挑战</t>
+          <t>增强灵气</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -1704,14 +1698,14 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" s="8">
       <c r="A16" s="33" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B16" s="33" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>炼器材料</t>
+          <t>永久挑战</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -1722,35 +1716,65 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" s="8">
       <c r="A17" s="33" t="n">
+        <v>262</v>
+      </c>
+      <c r="B17" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>炼器材料</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>hero_all</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="n">
         <v>830</v>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B18" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="33" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>兽潮来袭</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
+      <c r="D18" s="17" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
         <v>901</v>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B19" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>剧情测试</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>hero_all</t>
         </is>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>902</v>
+      </c>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>兽潮来袭</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1 A3:A4 A15:A1048576">
@@ -1773,7 +1797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.875" customWidth="1" style="9" min="1" max="1"/>
@@ -2996,6 +3020,98 @@
         </is>
       </c>
       <c r="L34" s="41" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>262006</v>
+      </c>
+      <c r="B35" s="42" t="n">
+        <v>830</v>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>兽潮来袭·一</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="n"/>
+      <c r="E35" s="0" t="n"/>
+      <c r="F35" s="25" t="n"/>
+      <c r="G35" s="25" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="n"/>
+      <c r="I35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L35" s="41" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>262007</v>
+      </c>
+      <c r="B36" s="42" t="n">
+        <v>830</v>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>兽潮来袭·二</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="0" t="n"/>
+      <c r="F36" s="25" t="n"/>
+      <c r="G36" s="25" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="n"/>
+      <c r="I36" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="11" t="n"/>
+      <c r="K36" s="41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L36" s="41" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>262008</v>
+      </c>
+      <c r="B37" s="42" t="n">
+        <v>830</v>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>兽潮来袭·三</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="n"/>
+      <c r="E37" s="0" t="n"/>
+      <c r="F37" s="25" t="n"/>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="H37" s="29" t="n"/>
+      <c r="I37" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="11" t="n"/>
+      <c r="K37" s="41" t="n"/>
+      <c r="L37" s="41" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B2">

--- a/resources/quest/quest.xlsx
+++ b/resources/quest/quest.xlsx
@@ -1438,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="15" customWidth="1" style="33" min="1" max="2"/>
@@ -1506,26 +1506,32 @@
     </row>
     <row r="5" ht="16.5" customHeight="1" s="8">
       <c r="A5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="B5" s="24" t="n"/>
+        <v>250</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>兽潮来袭·一</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="n"/>
+          <t>服丹飞升</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>hero_all</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="8">
       <c r="A6" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="B6" s="24" t="n">
+        <v>251</v>
+      </c>
+      <c r="B6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>服丹飞升</t>
+          <t>以战养战</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -1536,14 +1542,14 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" s="8">
       <c r="A7" s="23" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>以战养战</t>
+          <t>炼丹自由</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -1554,14 +1560,14 @@
     </row>
     <row r="8" ht="16.5" customHeight="1" s="8">
       <c r="A8" s="23" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>炼丹自由</t>
+          <t>道袍加身</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -1572,14 +1578,14 @@
     </row>
     <row r="9" ht="16.5" customHeight="1" s="8">
       <c r="A9" s="23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>道袍加身</t>
+          <t>真仙助我</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -1590,14 +1596,14 @@
     </row>
     <row r="10" ht="16.5" customHeight="1" s="8">
       <c r="A10" s="23" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>真仙助我</t>
+          <t>灵气福地</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -1608,14 +1614,14 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" s="8">
       <c r="A11" s="23" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>灵气福地</t>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>一分为二</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -1626,17 +1632,17 @@
     </row>
     <row r="12" ht="16.5" customHeight="1" s="8">
       <c r="A12" s="23" t="n">
-        <v>256</v>
-      </c>
-      <c r="B12" s="11" t="n">
+        <v>257</v>
+      </c>
+      <c r="B12" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="34" t="inlineStr">
-        <is>
-          <t>一分为二</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>结束任务测试</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>hero_all</t>
         </is>
@@ -1644,50 +1650,50 @@
     </row>
     <row r="13" ht="16.5" customHeight="1" s="8">
       <c r="A13" s="23" t="n">
-        <v>257</v>
-      </c>
-      <c r="B13" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>结束任务测试</t>
+        <v>258</v>
+      </c>
+      <c r="B13" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>打一次灵脉</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
+          <t>hero_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="8">
+      <c r="A14" s="33" t="n">
+        <v>260</v>
+      </c>
+      <c r="B14" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>增强灵气</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
           <t>hero_all</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" s="8">
-      <c r="A14" s="23" t="n">
-        <v>258</v>
-      </c>
-      <c r="B14" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>打一次灵脉</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>hero_1</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="8">
       <c r="A15" s="33" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B15" s="33" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>增强灵气</t>
+          <t>永久挑战</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -1698,14 +1704,14 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" s="8">
       <c r="A16" s="33" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B16" s="33" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>永久挑战</t>
+          <t>炼器材料</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -1715,15 +1721,15 @@
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="8">
-      <c r="A17" s="33" t="n">
-        <v>262</v>
-      </c>
-      <c r="B17" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="33" t="inlineStr">
-        <is>
-          <t>炼器材料</t>
+      <c r="A17" s="23" t="n">
+        <v>901</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>剧情测试</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -1734,47 +1740,19 @@
     </row>
     <row r="18">
       <c r="A18" s="33" t="n">
-        <v>830</v>
-      </c>
-      <c r="B18" s="33" t="n">
-        <v>1</v>
-      </c>
+        <v>910</v>
+      </c>
+      <c r="B18" s="33" t="n"/>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>兽潮来袭</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>901</v>
-      </c>
-      <c r="B19" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>剧情测试</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
+          <t>试炼之路</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>hero_all</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="n">
-        <v>902</v>
-      </c>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>兽潮来袭</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1 A3:A4 A15:A1048576">
@@ -1797,7 +1775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.875" customWidth="1" style="9" min="1" max="1"/>
@@ -2952,166 +2930,42 @@
         <v>262003</v>
       </c>
       <c r="B32" s="42" t="n">
-        <v>830</v>
+        <v>910</v>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>兽潮来袭·三环</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="n"/>
+          <t>试炼之一</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>通关试炼战场</t>
+        </is>
+      </c>
       <c r="E32" s="0" t="n"/>
-      <c r="F32" s="25" t="n"/>
-      <c r="G32" s="25" t="n"/>
+      <c r="F32" s="25" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="G32" s="25" t="inlineStr">
+        <is>
+          <t>{"combat_id":91001,"count":1}</t>
+        </is>
+      </c>
       <c r="H32" s="29" t="n"/>
       <c r="I32" s="30" t="n"/>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="41" t="n"/>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>92001</t>
+        </is>
+      </c>
+      <c r="K32" s="41" t="inlineStr">
+        <is>
+          <t>81002</t>
+        </is>
+      </c>
       <c r="L32" s="41" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="n">
-        <v>262004</v>
-      </c>
-      <c r="B33" s="42" t="n">
-        <v>830</v>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>兽潮来袭·二环</t>
-        </is>
-      </c>
-      <c r="D33" s="25" t="n"/>
-      <c r="E33" s="0" t="n"/>
-      <c r="F33" s="25" t="n"/>
-      <c r="G33" s="25" t="n"/>
-      <c r="H33" s="29" t="n"/>
-      <c r="I33" s="30" t="n"/>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="41" t="inlineStr">
-        <is>
-          <t>262003</t>
-        </is>
-      </c>
-      <c r="L33" s="41" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="n">
-        <v>262005</v>
-      </c>
-      <c r="B34" s="42" t="n">
-        <v>830</v>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>兽潮来袭·一环</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="n"/>
-      <c r="E34" s="0" t="n"/>
-      <c r="F34" s="25" t="n"/>
-      <c r="G34" s="25" t="n"/>
-      <c r="H34" s="29" t="n"/>
-      <c r="I34" s="30" t="n"/>
-      <c r="J34" s="11" t="n"/>
-      <c r="K34" s="41" t="inlineStr">
-        <is>
-          <t>262004</t>
-        </is>
-      </c>
-      <c r="L34" s="41" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="n">
-        <v>262006</v>
-      </c>
-      <c r="B35" s="42" t="n">
-        <v>830</v>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>兽潮来袭·一</t>
-        </is>
-      </c>
-      <c r="D35" s="25" t="n"/>
-      <c r="E35" s="0" t="n"/>
-      <c r="F35" s="25" t="n"/>
-      <c r="G35" s="25" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="H35" s="29" t="n"/>
-      <c r="I35" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="11" t="n"/>
-      <c r="K35" s="41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L35" s="41" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="n">
-        <v>262007</v>
-      </c>
-      <c r="B36" s="42" t="n">
-        <v>830</v>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>兽潮来袭·二</t>
-        </is>
-      </c>
-      <c r="D36" s="25" t="n"/>
-      <c r="E36" s="0" t="n"/>
-      <c r="F36" s="25" t="n"/>
-      <c r="G36" s="25" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n"/>
-      <c r="I36" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="11" t="n"/>
-      <c r="K36" s="41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="L36" s="41" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="n">
-        <v>262008</v>
-      </c>
-      <c r="B37" s="42" t="n">
-        <v>830</v>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>兽潮来袭·三</t>
-        </is>
-      </c>
-      <c r="D37" s="25" t="n"/>
-      <c r="E37" s="0" t="n"/>
-      <c r="F37" s="25" t="n"/>
-      <c r="G37" s="25" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="H37" s="29" t="n"/>
-      <c r="I37" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="11" t="n"/>
-      <c r="K37" s="41" t="n"/>
-      <c r="L37" s="41" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B2">
